--- a/文档/Hediff/损伤Hediff与触发逻辑.xlsx
+++ b/文档/Hediff/损伤Hediff与触发逻辑.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="11655" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Hediff总览" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,48 +11,206 @@
     <sheet name="触发逻辑" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="26">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FF1F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <sz val="10"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -62,26 +219,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FF2F5496"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FC"/>
+        <fgColor rgb="FFF2F6FC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -91,21 +438,168 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
       </left>
       <right/>
       <top/>
@@ -113,34 +607,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -148,97 +618,265 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -591,7 +1229,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -601,443 +1238,484 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Rim-Hormones 透支损伤 Hediff 总览（2026-07-28 创建）</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>defName</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>附着部件</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>触发活动</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>恢复机制</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>恢复速度</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>一、肌肉劳损类</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>LaborMuscleStrain</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>肌肉劳损</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Arm / Leg（左右独立）</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>采矿/砍树/搬运等重体力劳作</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Disappears 60000t</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>1 游戏天后消失</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>重体力透支：疲劳→拉伤→撕裂</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>一、肌肉劳损类</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>DiggingMuscleStrain</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>肩背劳损</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Arm(主手)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>挖掘（锄头动作，肩+脊柱联动）</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Disappears 60000t</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>1 游戏天后消失</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Spine 用 Moving 代偿：酸痛→肩袖损伤→肩关节脱位</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>二、心肺爆发类</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>CardioOverexert</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>心肺透支</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Heart</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>逃跑/冲刺/追逐等爆发运动</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>SeverityPerDay -0.36</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>约 3 天回落满级</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>心悸→心律失常→心肌缺氧/肺水肿</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>二、心肺爆发类</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>SuffocationStrain</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>缺氧损伤</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Lung</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>窒息/溺水后恢复</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>SeverityPerDay -0.36</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>约 3 天回落满级</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>肺部灼热→呼吸困难→肺水肿</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>三、关节韧带类</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>CombatJointStrain</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>关节劳损</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Arm / Hand / Foot（共享）</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>近战搏斗/举砍/扭转动作</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Disappears 60000t</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>1 游戏天后消失</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>扭伤→韧带损伤→关节脱位</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="33" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>三、关节韧带类</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>FallJointStrain</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>扭伤</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Leg</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>摔倒/扭伤（腿+脊柱复合）</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Disappears 60000t</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>1 游戏天后消失</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Spine 用 Consciousness/Moving 代偿：踝扭伤→膝伤腰拉→脊柱挫伤</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>四、神经代谢类</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>CombatEnduranceExhaust</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>神经耗竭</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Brain</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>长时间高强度战斗(&gt;3分钟)</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>SeverityPerDay -0.12</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>约 8 天回落满级(极慢)</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>神经兴奋(初期正向)→抑制→耗竭</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>四、神经代谢类</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>MetabolicExhaust</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>代谢透支</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Stomach / Liver</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>肾上腺素 High 长期积压</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>SeverityPerDay -0.12</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>约 8 天回落满级(极慢)</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>代谢紊乱→消化抑制→器官过载，显著加剧饥饿</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>五、感官过载类</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>SensoryOverload</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>感官过载</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Eye / Ear（两侧共享）</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>爆炸/枪击/高强度战斗</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>VisualStrain</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>视觉过载</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Eye（两眼独立）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>爆炸闪光/强光刺激</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>SeverityPerDay -0.29</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>约 3.5 天回落满级</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>视觉疲劳耳鸣→眼肌痉挛听觉过敏→视网膜/听力损伤</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>视觉疲劳→眼肌痉挛→视网膜损伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>五、感官过载类</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>AuditoryStrain</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>听觉过载</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Ear（两耳独立）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>持续枪声/爆炸声</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>SeverityPerDay -0.29</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>约 3.5 天回落满级</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>耳鸣→听觉过敏→听力损伤（内耳前庭联动意识）</t>
         </is>
       </c>
     </row>
@@ -1055,8 +1733,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -1069,1043 +1747,1152 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>各 Hediff 三阶段详情（severity 0 / 0.4 / 0.75；数值为乘算系数）</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>defName</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>起始severity</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>阶段名</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>疼痛偏移</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>属性修正(statFactors)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>能力修正(capMods)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>LaborMuscleStrain</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>肌肉疲劳</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>+0.02</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Manipulation ×0.95, Moving ×0.95</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>肌肉拉伤</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>+0.08</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>Manipulation ×0.85, Moving ×0.85</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n"/>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>肌肉撕裂</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>+0.20</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Manipulation ×0.70, Moving ×0.70</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>DiggingMuscleStrain</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>肩部酸痛</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>+0.03</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>Manipulation ×0.92, Moving ×0.97</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>肩袖损伤</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>+0.10</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>Manipulation ×0.80, Moving ×0.92</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>肩关节脱位</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>+0.25</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Manipulation ×0.60, Moving ×0.88</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>CardioOverexert</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>心悸</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>BloodPumping ×1.1, Breathing ×1.05</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>初期为兴奋期(略增强)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="7" t="inlineStr">
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>心律失常与过度换气</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>MoveSpeed ×0.90</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>BloodPumping ×0.85, Breathing ×0.85</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="33" customHeight="1">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>心肌缺氧与肺水肿</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>MoveSpeed ×0.75</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>BloodPumping ×0.70, Breathing ×0.65, Consciousness ×0.85</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>SuffocationStrain</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>肺部灼热</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>Breathing ×0.90, BloodPumping ×0.95</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>呼吸困难</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>MoveSpeed ×0.92</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>Breathing ×0.75, BloodPumping ×0.85</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="n"/>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr"/>
+    </row>
+    <row r="14" ht="33" customHeight="1">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>肺水肿</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>Breathing ×0.60, BloodPumping ×0.70, Consciousness ×0.80</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>CombatJointStrain</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>关节扭伤</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>+0.03</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>MoveSpeed ×0.92</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Manipulation ×0.95</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>韧带损伤</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>+0.12</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>MoveSpeed ×0.80</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>Manipulation ×0.80</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>关节脱位</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>+0.25</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>MoveSpeed ×0.60</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Manipulation ×0.65</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>FallJointStrain</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>踝关节扭伤</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>+0.05</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>Moving ×0.90</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>膝关节扭伤与腰背拉伤</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>+0.15</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="18" t="inlineStr">
         <is>
           <t>Moving ×0.75, Manipulation ×0.85</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="n"/>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="H19" s="18" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>脊柱挫伤与腿部韧带撕裂</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>+0.30</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>Moving ×0.60, Consciousness ×0.90</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="H20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>CombatEnduranceExhaust</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>神经兴奋</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>-0.05</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Sight ×1.05, Consciousness ×1.05</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>初期正向：减痛+感知增强</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="7" t="inlineStr">
+    <row r="22" ht="16.5" customHeight="1">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>神经抑制</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>Sight ×0.90, Consciousness ×0.85</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>神经耗竭</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>+0.10</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>MentalBreakThreshold ×1.3</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Sight ×0.70, Consciousness ×0.70</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>更易精神崩溃</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="24" ht="16.5" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>MetabolicExhaust</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>代谢紊乱</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>Metabolism ×1.15, BloodFiltration ×1.05</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>hungerRateFactor ×1.2</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="9" t="inlineStr">
+    <row r="25" ht="16.5" customHeight="1">
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>消化抑制</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>Metabolism ×0.80, BloodFiltration ×0.90</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="18" t="inlineStr">
         <is>
           <t>hungerRateFactor ×1.35</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="13" t="n"/>
-      <c r="B26" s="9" t="inlineStr">
+    <row r="26" ht="33" customHeight="1">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>器官过载</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>Metabolism ×0.60, BloodFiltration ×0.70, BloodPumping ×0.80</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>hungerRateFactor ×1.5</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>SensoryOverload</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+    <row r="27" ht="16.5" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>VisualStrain</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>轻</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>视觉疲劳与耳鸣</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>视觉疲劳</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>+0.02</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Sight ×0.90, Hearing ×0.85</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>Sight ×0.90</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>眼肌痉挛与听觉过敏</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>眼肌痉挛</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>+0.08</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Sight ×0.75, Hearing ×0.65, Consciousness ×0.95</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="n"/>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Sight ×0.75</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>拆分样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>重</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>视网膜与听力损伤</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>视网膜损伤</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>+0.15</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Sight ×0.50, Hearing ×0.40, Consciousness ×0.80</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr"/>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Sight ×0.50</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>AuditoryStrain</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>轻</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>耳鸣</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>+0.02</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>Hearing ×0.85</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16.5" customHeight="1">
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>听觉过敏</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>+0.08</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>Hearing ×0.65, Consciousness ×0.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33" customHeight="1">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>重</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>听力损伤</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>Hearing ×0.40, Consciousness ×0.80</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A30:A32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A9:A11"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A9:A11"/>
     <mergeCell ref="A27:A29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2119,7 +2906,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
@@ -2128,1270 +2915,1270 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>损伤触发计算逻辑（两条路径）</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>路径一：劳作累积（日常工作 → 肌肉/关节劳损）</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>环节</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>公式 / 规则</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>关键参数</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4" ht="33" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>累计周期</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>每 tick 命中工作白名单则 workTickAccumulator += 1，满 WorkTicksPerSettle 结算一次</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>WorkTicksPerSettle = 400t (≈6.6s)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>余数跨 Job/跨存档保留</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="33" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>赶路排除</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>静态工作(挖矿/砍树/种植等) pather.Moving 时不累加；仅 Haul* 属移动型劳作照常累加</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>IsMobileWork 白名单 = Haul*</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>打猎已从白名单移除</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>体魄经验</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Learn(Physique, xp × factor)</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>每次结算给体魄加经验</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="7" ht="33" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>劳损扣减</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>finalStrain = strain(基础) × factor × consumeMult(阶段)；CurLevel -= finalStrain (下限0)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>consumeMult: 虚弱2.0/普通1.0/健康0.75/强壮0.5/巅峰0.3</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Need 是剩余体力储备，越强越耐劳</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="8" ht="33" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>拉伤概率(核心)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>finalChance = chance(基础) × factor × chanceMult_stage × chanceMult_setting</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>chanceMult_stage: 虚弱1.25/普通1.0/健康0.75/强壮0.5/巅峰0.25</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>setting 默认1.0</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9" ht="33" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>前置门槛</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>canTrigger = CurLevel &lt; MaxLevel × thresholdPct；triggered = canTrigger &amp;&amp; Rand.Value &lt; finalChance</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>thresholdPct 默认0.10；MaxLevel:虚弱650/普通1000/健康1250/强壮2000/巅峰3000</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>体力储备须先掉到10%以下才可能拉伤</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>触发后果</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>随机选一条 Arm/Leg，对 LaborMuscleStrain 累加 +0.35 severity</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>阶段边界 0/0.4/0.75，约3次到重度封顶1.0</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>TryAddMuscleStrain</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>各工作基础值（strain / chance，每 400t 周期）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>工作类型</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>strain(体力扣减)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>chance(拉伤基础概率)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="14" ht="16.5" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>挖矿 Mine</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>最高强度</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>砍树/拆除/平整/深钻等</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>3~4%</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>重体力</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>搬运Haul/宰杀/打猎/修理</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>1~3%</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>中等；搬运属移动型</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="17" ht="33" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>种植/收割/割草 Sow/Harvest/CutPlant</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>轻体力</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="19" ht="16.5" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>路径二：战斗肾上腺素透支（近战 + 射击 → 随机损伤池）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>环节</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>公式 / 规则</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>关键参数</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="21" ht="33" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>触发入口</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>近战 Verb_MeleeAttack.TryCastShot + 射击 Verb_LaunchProjectile.TryCastShot</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>射击为本次新增(概率×0.5)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="22" ht="16.5" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>当前 Adrenaline.Severity ≥ 中档阈值 且 未豁免(IsAdrenalineExempt)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>AdrenalineThresholdMedium</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>射击本身不产肾上腺素，需先积累到High</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="23" ht="16.5" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>触发概率</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>chance = (0.2 + 0.04 × (13 − physiqueLevel)) × chanceMultiplier</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>近战 chanceMultiplier=1.0；射击=0.5</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>体魄越低概率越高，13级起豁免</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="24" ht="16.5" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>损伤分档</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>roll=Rand.Value 按体魄档决定 轻/中/重 比例</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>见下表</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>physiqueLevel 分 &lt;5 / 5-7 / ≥8 三档</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25" ht="33" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>触发后果</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>命中新建对应 Hediff，初始 Severity = 0.3 + Rand×0.4 (即0.3~0.7)，并附着到映射器官</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>部件映射见Hediff总览</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>已修复：不再全加到全身</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="27" ht="16.5" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>体魄档 → 轻/中/重损伤抽取比例</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>体魄等级</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>重度 (roll&lt;)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>中度 (roll&lt;)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>轻度 (其余)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="29" ht="16.5" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>&lt; 5</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>剩余</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="30" ht="16.5" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>5 – 7</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>剩余</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="31" ht="16.5" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>≥ 8</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>剩余</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="33" ht="16.5" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>损伤池构成（当前抽取列表）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>档位</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>包含 Hediff</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="35" ht="16.5" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>轻度</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>LaborMuscleStrain, CombatJointStrain</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>肌肉/关节</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36" ht="16.5" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>中度</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>CardioOverexert, SuffocationStrain</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>心/肺</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="37" ht="16.5" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>重度</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>CombatEnduranceExhaust, FallJointStrain</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>脑(神经)/腿</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="38" ht="16.5" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>未入池</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>SensoryOverload, MetabolicExhaust</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>已定义但战斗透支暂不抽取(可后续加入)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>【补充】战斗透支损伤——生成逻辑与最终概率（按实际代码公式算出）</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n"/>
-      <c r="C41" s="15" t="n"/>
-      <c r="D41" s="15" t="n"/>
-      <c r="E41" s="16" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="8" t="n"/>
     </row>
     <row r="42" ht="60" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>生成分两步：①【是否触发】每次近战/射击攻击后，若当前肾上腺素≥中档且未豁免(体魄≥13豁免)，按 chance=(0.2+0.04×(13−体魄))×倍率 掷骰(近战倍率1.0/射击0.5)；②【抽哪种】触发后按体魄档(&lt;5 / 5–7 / ≥8)决定轻/中/重比例，再在该档 2 个 Hediff 中等概率各选其一(每个占该档一半)。故『单次攻击生成某具体损伤』的概率 = 触发概率 × 该档档位比例 × 0.5。</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="8" t="n"/>
+    </row>
+    <row r="44" ht="16.5" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>表A　各体魄等级 → 单次攻击最终触发概率（第①步）</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="15" t="n"/>
-      <c r="D44" s="15" t="n"/>
-      <c r="E44" s="16" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="8" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>体魄等级</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>近战触发概率</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>射击触发概率</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>所属体魄档</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="19" t="inlineStr">
+    <row r="46" ht="27" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>体魄 0</t>
         </is>
       </c>
-      <c r="B46" s="19" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="C46" s="19" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>&lt;5（弱）</t>
         </is>
       </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>体魄越低越易透支</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="19" t="inlineStr">
+    <row r="47" ht="27" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>体魄 3</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>&lt;5（弱）</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>体魄越低越易透支</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="19" t="inlineStr">
+    <row r="48" ht="27" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>体魄 5</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="D48" s="19" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>5–7（中）</t>
         </is>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>体魄越低越易透支</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
+    <row r="49" ht="27" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>体魄 7</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="D49" s="19" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>5–7（中）</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>体魄越低越易透支</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr">
+    <row r="50" ht="27" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>体魄 8</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>≥8（强）</t>
         </is>
       </c>
-      <c r="E50" s="20" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>体魄越低越易透支</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>体魄 10</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D51" s="19" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>≥8（强）</t>
         </is>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>体魄越低越易透支</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="52" ht="27" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>体魄 12</t>
         </is>
       </c>
-      <c r="B52" s="19" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="C52" s="19" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="D52" s="19" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>≥8（强）</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>体魄越低越易透支</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+    <row r="53" ht="54" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>体魄 ≥13</t>
         </is>
       </c>
-      <c r="B53" s="19" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>0%（豁免）</t>
         </is>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>0%（豁免）</t>
         </is>
       </c>
-      <c r="D53" s="19" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>达到豁免阈值，战斗透支完全不触发</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+    <row r="55" ht="16.5" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>表B　触发后 → 各损伤被抽中概率（第②步，与体魄档相关）</t>
         </is>
       </c>
-      <c r="B55" s="15" t="n"/>
-      <c r="C55" s="15" t="n"/>
-      <c r="D55" s="15" t="n"/>
-      <c r="E55" s="16" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="8" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>体魄档</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>轻度合计→单个</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>中度合计→单个</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>重度合计→单个</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>损伤对应</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="19" t="inlineStr">
+    <row r="57" ht="175.5" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>&lt;5（弱）</t>
         </is>
       </c>
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>40% → 各 20%</t>
         </is>
       </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>30% → 各 15%</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>30% → 各 15%</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>轻:Labor/CombatJoint  中:Cardio/Suffocation  重:CombatEndurance/FallJoint</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="19" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>5–7（中）</t>
         </is>
       </c>
-      <c r="B58" s="19" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>50% → 各 25%</t>
         </is>
       </c>
-      <c r="C58" s="19" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>35% → 各 18%</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr">
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>15% → 各 8%</t>
         </is>
       </c>
-      <c r="E58" s="20" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>（同上）</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>≥8（强）</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>70% → 各 35%</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>25% → 各 12%</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>5% → 各 2%</t>
         </is>
       </c>
-      <c r="E59" s="20" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>（同上）</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+    <row r="62" ht="16.5" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>表C　综合：单次【近战】攻击生成某具体损伤的总概率 = 触发概率 × 档位比例 × 0.5</t>
         </is>
       </c>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="15" t="n"/>
-      <c r="D62" s="15" t="n"/>
-      <c r="E62" s="16" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="8" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>体魄等级</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>任一轻度损伤(单个)</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>任一中度损伤(单个)</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>任一重度损伤(单个)</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="19" t="inlineStr">
+    <row r="64" ht="27" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>体魄 0</t>
         </is>
       </c>
-      <c r="B64" s="19" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>14.40%</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>10.80%</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D64" s="11" t="inlineStr">
         <is>
           <t>10.80%</t>
         </is>
       </c>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>射击=此值×0.5</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="19" t="inlineStr">
+    <row r="65" ht="27" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>体魄 3</t>
         </is>
       </c>
-      <c r="B65" s="19" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>12.00%</t>
         </is>
       </c>
-      <c r="C65" s="19" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>9.00%</t>
         </is>
       </c>
-      <c r="D65" s="19" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>9.00%</t>
         </is>
       </c>
-      <c r="E65" s="20" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>射击=此值×0.5</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="19" t="inlineStr">
+    <row r="66" ht="27" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>体魄 5</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>13.00%</t>
         </is>
       </c>
-      <c r="C66" s="19" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>9.10%</t>
         </is>
       </c>
-      <c r="D66" s="19" t="inlineStr">
+      <c r="D66" s="11" t="inlineStr">
         <is>
           <t>3.90%</t>
         </is>
       </c>
-      <c r="E66" s="20" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>射击=此值×0.5</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="19" t="inlineStr">
+    <row r="67" ht="27" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>体魄 7</t>
         </is>
       </c>
-      <c r="B67" s="19" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>11.00%</t>
         </is>
       </c>
-      <c r="C67" s="19" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>7.70%</t>
         </is>
       </c>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>3.30%</t>
         </is>
       </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>射击=此值×0.5</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
+    <row r="68" ht="27" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>体魄 8</t>
         </is>
       </c>
-      <c r="B68" s="19" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>14.00%</t>
         </is>
       </c>
-      <c r="C68" s="19" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>5.00%</t>
         </is>
       </c>
-      <c r="D68" s="19" t="inlineStr">
+      <c r="D68" s="11" t="inlineStr">
         <is>
           <t>1.00%</t>
         </is>
       </c>
-      <c r="E68" s="20" t="inlineStr">
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>射击=此值×0.5</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="19" t="inlineStr">
+    <row r="69" ht="27" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>体魄 10</t>
         </is>
       </c>
-      <c r="B69" s="19" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>11.20%</t>
         </is>
       </c>
-      <c r="C69" s="19" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>4.00%</t>
         </is>
       </c>
-      <c r="D69" s="19" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>0.80%</t>
         </is>
       </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>射击=此值×0.5</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="19" t="inlineStr">
+    <row r="70" ht="27" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>体魄 12</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>8.40%</t>
         </is>
       </c>
-      <c r="C70" s="19" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>3.00%</t>
         </is>
       </c>
-      <c r="D70" s="19" t="inlineStr">
+      <c r="D70" s="11" t="inlineStr">
         <is>
           <t>0.60%</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>射击=此值×0.5</t>
         </is>
       </c>
     </row>
     <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="17" t="inlineStr">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>说明：①以上均为『单次攻击』概率，实战每场战斗有多次攻击，累积生成率远高于单次值。②同一部件已有该损伤则不重复叠加(按部件判重)。③SensoryOverload / MetabolicExhaust 已定义但未纳入战斗抽取池，故战斗不会生成。④劳作路径的拉伤概率见上文表(finalChance=基础chance×factor×阶段系数×设置，且体力储备须先&lt;10%)。</t>
         </is>
       </c>
-      <c r="B72" s="15" t="n"/>
-      <c r="C72" s="15" t="n"/>
-      <c r="D72" s="15" t="n"/>
-      <c r="E72" s="16" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3403,9 +4190,9 @@
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
